--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129719126</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129726111</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129726009</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129719496</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129720327</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>129726153</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129725784</v>
+        <v>129726121</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584306</v>
+        <v>584219</v>
       </c>
       <c r="R8" t="n">
-        <v>6400876</v>
+        <v>6401024</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726121</v>
+        <v>129725784</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584219</v>
+        <v>584306</v>
       </c>
       <c r="R9" t="n">
-        <v>6401024</v>
+        <v>6400876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,56 +1556,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725840</v>
+        <v>129719199</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>96365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584291</v>
+        <v>584216</v>
       </c>
       <c r="R10" t="n">
-        <v>6400891</v>
+        <v>6400895</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,40 +1624,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129719199</v>
+        <v>129719187</v>
       </c>
       <c r="B11" t="n">
-        <v>96364</v>
+        <v>92870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,37 +1674,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584216</v>
+        <v>584220</v>
       </c>
       <c r="R11" t="n">
-        <v>6400895</v>
+        <v>6400901</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,57 +1779,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129719187</v>
+        <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584220</v>
+        <v>584291</v>
       </c>
       <c r="R12" t="n">
-        <v>6400901</v>
+        <v>6400891</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1846,96 +1855,87 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129719984</v>
+        <v>129719583</v>
       </c>
       <c r="B13" t="n">
-        <v>96364</v>
+        <v>91609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584188</v>
+        <v>584209</v>
       </c>
       <c r="R13" t="n">
-        <v>6400848</v>
+        <v>6400866</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,57 +2001,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129719583</v>
+        <v>129719984</v>
       </c>
       <c r="B14" t="n">
-        <v>91608</v>
+        <v>96365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584209</v>
+        <v>584188</v>
       </c>
       <c r="R14" t="n">
-        <v>6400866</v>
+        <v>6400848</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726185</v>
+        <v>129726204</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584229</v>
+        <v>584205</v>
       </c>
       <c r="R15" t="n">
-        <v>6401013</v>
+        <v>6401040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726214</v>
+        <v>129726185</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584178</v>
+        <v>584229</v>
       </c>
       <c r="R16" t="n">
-        <v>6400881</v>
+        <v>6401013</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726204</v>
+        <v>129726214</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584205</v>
+        <v>584178</v>
       </c>
       <c r="R17" t="n">
-        <v>6401040</v>
+        <v>6400881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2438,7 +2438,7 @@
         <v>129725705</v>
       </c>
       <c r="B18" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>129719448</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129719258</v>
+        <v>129726099</v>
       </c>
       <c r="B20" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,29 +2684,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584215</v>
+        <v>584229</v>
       </c>
       <c r="R20" t="n">
-        <v>6400897</v>
+        <v>6401032</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,49 +2732,40 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726099</v>
+        <v>129719258</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,28 +2790,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584229</v>
+        <v>584215</v>
       </c>
       <c r="R21" t="n">
-        <v>6401032</v>
+        <v>6400897</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2848,30 +2839,39 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
         <v>129725819</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129725803</v>
       </c>
       <c r="B23" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129726168</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>129726194</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129718908</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129726049</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129725774</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3630,10 +3630,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129726072</v>
+        <v>129719185</v>
       </c>
       <c r="B29" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3658,28 +3658,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584237</v>
+        <v>584220</v>
       </c>
       <c r="R29" t="n">
-        <v>6401043</v>
+        <v>6400901</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3706,40 +3707,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129719185</v>
+        <v>129726072</v>
       </c>
       <c r="B30" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,29 +3774,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584220</v>
+        <v>584237</v>
       </c>
       <c r="R30" t="n">
-        <v>6400901</v>
+        <v>6401043</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3813,39 +3822,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
         <v>129726136</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129726176</v>
       </c>
       <c r="B32" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>129719084</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129750113</v>
       </c>
       <c r="B34" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>129750075</v>
       </c>
       <c r="B35" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>129750063</v>
       </c>
       <c r="B36" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,44 +4498,44 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129750085</v>
+        <v>129750211</v>
       </c>
       <c r="B37" t="n">
-        <v>57895</v>
+        <v>56710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>100045</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>sträckande V</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584096</v>
+        <v>584363</v>
       </c>
       <c r="R37" t="n">
-        <v>6400801</v>
+        <v>6400913</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4575,12 +4575,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4607,44 +4617,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129750211</v>
+        <v>129750085</v>
       </c>
       <c r="B38" t="n">
-        <v>56709</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100045</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>sträckande V</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4654,13 +4664,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584363</v>
+        <v>584096</v>
       </c>
       <c r="R38" t="n">
-        <v>6400913</v>
+        <v>6400801</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4684,22 +4694,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -2435,56 +2435,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129725705</v>
+        <v>129719448</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>98769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 56162, Lilla fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584429</v>
+        <v>584201</v>
       </c>
       <c r="R18" t="n">
-        <v>6400936</v>
+        <v>6400891</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2511,9 +2512,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,69 +2539,68 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129719448</v>
+        <v>129725705</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla fårhult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584201</v>
+        <v>584429</v>
       </c>
       <c r="R19" t="n">
-        <v>6400891</v>
+        <v>6400936</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,19 +2627,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,12 +2644,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129719126</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129726111</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129719496</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129720327</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>129726153</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129726121</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>129725784</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129719199</v>
       </c>
       <c r="B10" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129719187</v>
       </c>
       <c r="B11" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,57 +1885,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129719583</v>
+        <v>129719984</v>
       </c>
       <c r="B13" t="n">
-        <v>91609</v>
+        <v>96370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584209</v>
+        <v>584188</v>
       </c>
       <c r="R13" t="n">
-        <v>6400866</v>
+        <v>6400848</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,57 +2001,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129719984</v>
+        <v>129719583</v>
       </c>
       <c r="B14" t="n">
-        <v>96365</v>
+        <v>91614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584188</v>
+        <v>584209</v>
       </c>
       <c r="R14" t="n">
-        <v>6400848</v>
+        <v>6400866</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,7 +2120,7 @@
         <v>129726204</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>129726185</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>129726214</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,57 +2435,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129719448</v>
+        <v>129725705</v>
       </c>
       <c r="B18" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla fårhult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584201</v>
+        <v>584429</v>
       </c>
       <c r="R18" t="n">
-        <v>6400891</v>
+        <v>6400936</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,19 +2511,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,68 +2528,69 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129725705</v>
+        <v>129719448</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 56162, Lilla fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584429</v>
+        <v>584201</v>
       </c>
       <c r="R19" t="n">
-        <v>6400936</v>
+        <v>6400891</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,9 +2617,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,12 +2644,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
         <v>129726099</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>129719258</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>129725819</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129725803</v>
       </c>
       <c r="B23" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129726168</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>129726194</v>
       </c>
       <c r="B25" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129718908</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129726049</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129725774</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129719185</v>
       </c>
       <c r="B29" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129726072</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726136</v>
       </c>
       <c r="B31" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129726176</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>129719084</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129750113</v>
       </c>
       <c r="B34" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>129750075</v>
       </c>
       <c r="B35" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>129750063</v>
       </c>
       <c r="B36" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -897,60 +897,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726009</v>
+        <v>129719496</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584277</v>
+        <v>584200</v>
       </c>
       <c r="R4" t="n">
-        <v>6400915</v>
+        <v>6400871</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,9 +974,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,19 +1001,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129719496</v>
+        <v>129720327</v>
       </c>
       <c r="B5" t="n">
         <v>98774</v>
@@ -1036,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1046,17 +1053,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584200</v>
+        <v>584280</v>
       </c>
       <c r="R5" t="n">
-        <v>6400871</v>
+        <v>6400833</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,57 +1129,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129720327</v>
+        <v>129726009</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584280</v>
+        <v>584277</v>
       </c>
       <c r="R6" t="n">
-        <v>6400833</v>
+        <v>6400915</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,19 +1209,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,12 +1226,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129719126</v>
+        <v>129726111</v>
       </c>
       <c r="B2" t="n">
         <v>98774</v>
@@ -703,29 +703,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584215</v>
+        <v>584229</v>
       </c>
       <c r="R2" t="n">
-        <v>6400918</v>
+        <v>6401025</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,46 +751,37 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726111</v>
+        <v>129719126</v>
       </c>
       <c r="B3" t="n">
         <v>98774</v>
@@ -819,28 +809,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584229</v>
+        <v>584215</v>
       </c>
       <c r="R3" t="n">
-        <v>6401025</v>
+        <v>6400918</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,87 +858,99 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129719496</v>
+        <v>129726009</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584200</v>
+        <v>584277</v>
       </c>
       <c r="R4" t="n">
-        <v>6400871</v>
+        <v>6400915</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,19 +977,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,19 +994,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129720327</v>
+        <v>129719496</v>
       </c>
       <c r="B5" t="n">
         <v>98774</v>
@@ -1043,7 +1036,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1053,17 +1046,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584280</v>
+        <v>584200</v>
       </c>
       <c r="R5" t="n">
-        <v>6400833</v>
+        <v>6400871</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,60 +1122,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726009</v>
+        <v>129720327</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584277</v>
+        <v>584280</v>
       </c>
       <c r="R6" t="n">
-        <v>6400915</v>
+        <v>6400833</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,9 +1199,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,12 +1226,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1885,57 +1885,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129719984</v>
+        <v>129726204</v>
       </c>
       <c r="B13" t="n">
-        <v>96370</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584188</v>
+        <v>584205</v>
       </c>
       <c r="R13" t="n">
-        <v>6400848</v>
+        <v>6401040</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,96 +1961,86 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129719583</v>
+        <v>129726185</v>
       </c>
       <c r="B14" t="n">
-        <v>91614</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584209</v>
+        <v>584229</v>
       </c>
       <c r="R14" t="n">
-        <v>6400866</v>
+        <v>6401013</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,46 +2067,37 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726204</v>
+        <v>129726214</v>
       </c>
       <c r="B15" t="n">
         <v>98774</v>
@@ -2160,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584205</v>
+        <v>584178</v>
       </c>
       <c r="R15" t="n">
-        <v>6401040</v>
+        <v>6400881</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,56 +2203,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726185</v>
+        <v>129719984</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>96370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584229</v>
+        <v>584188</v>
       </c>
       <c r="R16" t="n">
-        <v>6401013</v>
+        <v>6400848</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2299,86 +2280,96 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726214</v>
+        <v>129719583</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>91614</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584178</v>
+        <v>584209</v>
       </c>
       <c r="R17" t="n">
-        <v>6400881</v>
+        <v>6400866</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2405,30 +2396,39 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129726111</v>
+        <v>129719126</v>
       </c>
       <c r="B2" t="n">
         <v>98774</v>
@@ -703,28 +703,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584229</v>
+        <v>584215</v>
       </c>
       <c r="R2" t="n">
-        <v>6401025</v>
+        <v>6400918</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,37 +752,46 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129719126</v>
+        <v>129726111</v>
       </c>
       <c r="B3" t="n">
         <v>98774</v>
@@ -809,29 +819,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584215</v>
+        <v>584229</v>
       </c>
       <c r="R3" t="n">
-        <v>6400918</v>
+        <v>6401025</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,39 +867,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1885,56 +1885,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726204</v>
+        <v>129719984</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>96370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584205</v>
+        <v>584188</v>
       </c>
       <c r="R13" t="n">
-        <v>6401040</v>
+        <v>6400848</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,37 +1962,46 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726185</v>
+        <v>129726204</v>
       </c>
       <c r="B14" t="n">
         <v>98774</v>
@@ -2034,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584229</v>
+        <v>584205</v>
       </c>
       <c r="R14" t="n">
-        <v>6401013</v>
+        <v>6401040</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2107,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726214</v>
+        <v>129726185</v>
       </c>
       <c r="B15" t="n">
         <v>98774</v>
@@ -2140,10 +2150,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584178</v>
+        <v>584229</v>
       </c>
       <c r="R15" t="n">
-        <v>6400881</v>
+        <v>6401013</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,57 +2213,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129719984</v>
+        <v>129726214</v>
       </c>
       <c r="B16" t="n">
-        <v>96370</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584188</v>
+        <v>584178</v>
       </c>
       <c r="R16" t="n">
-        <v>6400848</v>
+        <v>6400881</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,39 +2289,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4498,44 +4498,44 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129750211</v>
+        <v>129750085</v>
       </c>
       <c r="B37" t="n">
-        <v>56710</v>
+        <v>57896</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100045</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>sträckande V</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584363</v>
+        <v>584096</v>
       </c>
       <c r="R37" t="n">
-        <v>6400913</v>
+        <v>6400801</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4575,22 +4575,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,44 +4607,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129750085</v>
+        <v>129750211</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>56710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100045</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>sträckande V</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4664,13 +4654,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584096</v>
+        <v>584363</v>
       </c>
       <c r="R38" t="n">
-        <v>6400801</v>
+        <v>6400913</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4694,12 +4684,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129719126</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129726111</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,60 +897,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726009</v>
+        <v>129719496</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584277</v>
+        <v>584200</v>
       </c>
       <c r="R4" t="n">
-        <v>6400915</v>
+        <v>6400871</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,9 +974,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +1001,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129719496</v>
+        <v>129720327</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1046,17 +1053,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584200</v>
+        <v>584280</v>
       </c>
       <c r="R5" t="n">
-        <v>6400871</v>
+        <v>6400833</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,57 +1129,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129720327</v>
+        <v>129726009</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584280</v>
+        <v>584277</v>
       </c>
       <c r="R6" t="n">
-        <v>6400833</v>
+        <v>6400915</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,19 +1209,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,12 +1226,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         <v>129726153</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129726121</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>129725784</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129719199</v>
+        <v>129719187</v>
       </c>
       <c r="B10" t="n">
-        <v>96370</v>
+        <v>92879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,37 +1567,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584216</v>
+        <v>584220</v>
       </c>
       <c r="R10" t="n">
-        <v>6400895</v>
+        <v>6400901</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129719187</v>
+        <v>129719199</v>
       </c>
       <c r="B11" t="n">
-        <v>92875</v>
+        <v>96374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,46 +1683,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584220</v>
+        <v>584216</v>
       </c>
       <c r="R11" t="n">
-        <v>6400901</v>
+        <v>6400895</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,7 +1782,7 @@
         <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>129719984</v>
       </c>
       <c r="B13" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,56 +2001,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726204</v>
+        <v>129719583</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>91618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584205</v>
+        <v>584209</v>
       </c>
       <c r="R14" t="n">
-        <v>6401040</v>
+        <v>6400866</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,40 +2078,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726185</v>
+        <v>129726204</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584229</v>
+        <v>584205</v>
       </c>
       <c r="R15" t="n">
-        <v>6401013</v>
+        <v>6401040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726214</v>
+        <v>129726185</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584178</v>
+        <v>584229</v>
       </c>
       <c r="R16" t="n">
-        <v>6400881</v>
+        <v>6401013</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,57 +2329,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129719583</v>
+        <v>129726214</v>
       </c>
       <c r="B17" t="n">
-        <v>91614</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584209</v>
+        <v>584178</v>
       </c>
       <c r="R17" t="n">
-        <v>6400866</v>
+        <v>6400881</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2396,95 +2405,87 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129725705</v>
+        <v>129719448</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 56162, Lilla fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584429</v>
+        <v>584201</v>
       </c>
       <c r="R18" t="n">
-        <v>6400936</v>
+        <v>6400891</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2511,9 +2512,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,69 +2539,68 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129719448</v>
+        <v>129725705</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla fårhult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584201</v>
+        <v>584429</v>
       </c>
       <c r="R19" t="n">
-        <v>6400891</v>
+        <v>6400936</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,19 +2627,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,12 +2644,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
         <v>129726099</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>129719258</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>129725819</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129725803</v>
       </c>
       <c r="B23" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129726168</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>129726194</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129718908</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129726049</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129725774</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129719185</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129726072</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726136</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129726176</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>129719084</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129750113</v>
       </c>
       <c r="B34" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>129750075</v>
       </c>
       <c r="B35" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>129750063</v>
       </c>
       <c r="B36" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,44 +4498,44 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129750085</v>
+        <v>129750211</v>
       </c>
       <c r="B37" t="n">
-        <v>57896</v>
+        <v>56710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>100045</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>sträckande V</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584096</v>
+        <v>584363</v>
       </c>
       <c r="R37" t="n">
-        <v>6400801</v>
+        <v>6400913</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4575,12 +4575,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4607,44 +4617,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129750211</v>
+        <v>129750085</v>
       </c>
       <c r="B38" t="n">
-        <v>56710</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100045</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>sträckande V</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4654,13 +4664,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584363</v>
+        <v>584096</v>
       </c>
       <c r="R38" t="n">
-        <v>6400913</v>
+        <v>6400801</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4684,22 +4694,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129719126</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129726111</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,57 +897,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129719496</v>
+        <v>129726009</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584200</v>
+        <v>584277</v>
       </c>
       <c r="R4" t="n">
-        <v>6400871</v>
+        <v>6400915</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,19 +977,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,22 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129720327</v>
+        <v>129719496</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1036,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1053,17 +1046,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584280</v>
+        <v>584200</v>
       </c>
       <c r="R5" t="n">
-        <v>6400833</v>
+        <v>6400871</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,60 +1122,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726009</v>
+        <v>129720327</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584277</v>
+        <v>584280</v>
       </c>
       <c r="R6" t="n">
-        <v>6400915</v>
+        <v>6400833</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,9 +1199,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,12 +1226,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         <v>129726153</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129726121</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>129725784</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129719187</v>
+        <v>129719199</v>
       </c>
       <c r="B10" t="n">
-        <v>92879</v>
+        <v>96376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,46 +1567,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584220</v>
+        <v>584216</v>
       </c>
       <c r="R10" t="n">
-        <v>6400901</v>
+        <v>6400895</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129719199</v>
+        <v>129719187</v>
       </c>
       <c r="B11" t="n">
-        <v>96374</v>
+        <v>92881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,37 +1674,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584216</v>
+        <v>584220</v>
       </c>
       <c r="R11" t="n">
-        <v>6400895</v>
+        <v>6400901</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,7 +1782,7 @@
         <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,57 +1885,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129719984</v>
+        <v>129719583</v>
       </c>
       <c r="B13" t="n">
-        <v>96374</v>
+        <v>91620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584188</v>
+        <v>584209</v>
       </c>
       <c r="R13" t="n">
-        <v>6400848</v>
+        <v>6400866</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,57 +2001,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129719583</v>
+        <v>129719984</v>
       </c>
       <c r="B14" t="n">
-        <v>91618</v>
+        <v>96376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584209</v>
+        <v>584188</v>
       </c>
       <c r="R14" t="n">
-        <v>6400866</v>
+        <v>6400848</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,7 +2120,7 @@
         <v>129726204</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>129726185</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>129726214</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,57 +2435,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129719448</v>
+        <v>129725705</v>
       </c>
       <c r="B18" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla fårhult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584201</v>
+        <v>584429</v>
       </c>
       <c r="R18" t="n">
-        <v>6400891</v>
+        <v>6400936</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,19 +2511,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,68 +2528,69 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129725705</v>
+        <v>129719448</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 56162, Lilla fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584429</v>
+        <v>584201</v>
       </c>
       <c r="R19" t="n">
-        <v>6400936</v>
+        <v>6400891</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,9 +2617,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,12 +2644,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
         <v>129726099</v>
       </c>
       <c r="B20" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>129719258</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>129725819</v>
       </c>
       <c r="B22" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129725803</v>
       </c>
       <c r="B23" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129726168</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>129726194</v>
       </c>
       <c r="B25" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129718908</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129726049</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129725774</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129719185</v>
       </c>
       <c r="B29" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129726072</v>
       </c>
       <c r="B30" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726136</v>
       </c>
       <c r="B31" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129726176</v>
       </c>
       <c r="B32" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>129719084</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129750113</v>
       </c>
       <c r="B34" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>129750075</v>
       </c>
       <c r="B35" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>129750063</v>
       </c>
       <c r="B36" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -4498,44 +4498,44 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129750211</v>
+        <v>129750085</v>
       </c>
       <c r="B37" t="n">
-        <v>56710</v>
+        <v>57896</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100045</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>sträckande V</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584363</v>
+        <v>584096</v>
       </c>
       <c r="R37" t="n">
-        <v>6400913</v>
+        <v>6400801</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4575,22 +4575,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,44 +4607,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129750085</v>
+        <v>129750211</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>56710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100045</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>sträckande V</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4664,13 +4654,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584096</v>
+        <v>584363</v>
       </c>
       <c r="R38" t="n">
-        <v>6400801</v>
+        <v>6400913</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4694,12 +4684,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -4498,44 +4498,44 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129750085</v>
+        <v>129750211</v>
       </c>
       <c r="B37" t="n">
-        <v>57896</v>
+        <v>56710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>100045</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>sträckande V</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584096</v>
+        <v>584363</v>
       </c>
       <c r="R37" t="n">
-        <v>6400801</v>
+        <v>6400913</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4575,12 +4575,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4607,44 +4617,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129750211</v>
+        <v>129750085</v>
       </c>
       <c r="B38" t="n">
-        <v>56710</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100045</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>sträckande V</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4654,13 +4664,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584363</v>
+        <v>584096</v>
       </c>
       <c r="R38" t="n">
-        <v>6400913</v>
+        <v>6400801</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4684,22 +4694,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129719126</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129726111</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129719496</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129720327</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>129726153</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726121</v>
+        <v>129725784</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584219</v>
+        <v>584306</v>
       </c>
       <c r="R8" t="n">
-        <v>6401024</v>
+        <v>6400876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129725784</v>
+        <v>129726121</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584306</v>
+        <v>584219</v>
       </c>
       <c r="R9" t="n">
-        <v>6400876</v>
+        <v>6401024</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129719199</v>
+        <v>129719187</v>
       </c>
       <c r="B10" t="n">
-        <v>96376</v>
+        <v>92881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,37 +1567,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584216</v>
+        <v>584220</v>
       </c>
       <c r="R10" t="n">
-        <v>6400895</v>
+        <v>6400901</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129719187</v>
+        <v>129719199</v>
       </c>
       <c r="B11" t="n">
-        <v>92881</v>
+        <v>96386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,46 +1683,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584220</v>
+        <v>584216</v>
       </c>
       <c r="R11" t="n">
-        <v>6400901</v>
+        <v>6400895</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,7 +1782,7 @@
         <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,57 +1885,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129719583</v>
+        <v>129726185</v>
       </c>
       <c r="B13" t="n">
-        <v>91620</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584209</v>
+        <v>584229</v>
       </c>
       <c r="R13" t="n">
-        <v>6400866</v>
+        <v>6401013</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,96 +1961,86 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129719984</v>
+        <v>129726204</v>
       </c>
       <c r="B14" t="n">
-        <v>96376</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584188</v>
+        <v>584205</v>
       </c>
       <c r="R14" t="n">
-        <v>6400848</v>
+        <v>6401040</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,49 +2067,40 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726204</v>
+        <v>129726214</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584205</v>
+        <v>584178</v>
       </c>
       <c r="R15" t="n">
-        <v>6401040</v>
+        <v>6400881</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,56 +2203,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726185</v>
+        <v>129719984</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>96386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584229</v>
+        <v>584188</v>
       </c>
       <c r="R16" t="n">
-        <v>6401013</v>
+        <v>6400848</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2299,86 +2280,96 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726214</v>
+        <v>129719583</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>91620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584178</v>
+        <v>584209</v>
       </c>
       <c r="R17" t="n">
-        <v>6400881</v>
+        <v>6400866</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2405,30 +2396,39 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
         <v>129719448</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726099</v>
+        <v>129719258</v>
       </c>
       <c r="B20" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,28 +2684,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584229</v>
+        <v>584215</v>
       </c>
       <c r="R20" t="n">
-        <v>6401032</v>
+        <v>6400897</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,40 +2733,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129719258</v>
+        <v>129726099</v>
       </c>
       <c r="B21" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,29 +2800,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584215</v>
+        <v>584229</v>
       </c>
       <c r="R21" t="n">
-        <v>6400897</v>
+        <v>6401032</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2839,39 +2848,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
         <v>129725819</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129725803</v>
       </c>
       <c r="B23" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129726168</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>129726194</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129718908</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129726049</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129725774</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129719185</v>
       </c>
       <c r="B29" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129726072</v>
       </c>
       <c r="B30" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726136</v>
       </c>
       <c r="B31" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129726176</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>129719084</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129750113</v>
       </c>
       <c r="B34" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>129750075</v>
       </c>
       <c r="B35" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>129750063</v>
       </c>
       <c r="B36" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -1556,57 +1556,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129719187</v>
+        <v>129725840</v>
       </c>
       <c r="B10" t="n">
-        <v>92881</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584220</v>
+        <v>584291</v>
       </c>
       <c r="R10" t="n">
-        <v>6400901</v>
+        <v>6400891</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,39 +1632,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1779,56 +1769,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725840</v>
+        <v>129719187</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>92881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584291</v>
+        <v>584220</v>
       </c>
       <c r="R12" t="n">
-        <v>6400891</v>
+        <v>6400901</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,86 +1846,96 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726185</v>
+        <v>129719583</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>91620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584229</v>
+        <v>584209</v>
       </c>
       <c r="R13" t="n">
-        <v>6401013</v>
+        <v>6400866</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,37 +1962,46 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726204</v>
+        <v>129726185</v>
       </c>
       <c r="B14" t="n">
         <v>98790</v>
@@ -2034,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584205</v>
+        <v>584229</v>
       </c>
       <c r="R14" t="n">
-        <v>6401040</v>
+        <v>6401013</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2107,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726214</v>
+        <v>129726204</v>
       </c>
       <c r="B15" t="n">
         <v>98790</v>
@@ -2140,10 +2150,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584178</v>
+        <v>584205</v>
       </c>
       <c r="R15" t="n">
-        <v>6400881</v>
+        <v>6401040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,57 +2213,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129719984</v>
+        <v>129726214</v>
       </c>
       <c r="B16" t="n">
-        <v>96386</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584188</v>
+        <v>584178</v>
       </c>
       <c r="R16" t="n">
-        <v>6400848</v>
+        <v>6400881</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,96 +2289,87 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129719583</v>
+        <v>129719984</v>
       </c>
       <c r="B17" t="n">
-        <v>91620</v>
+        <v>96386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584209</v>
+        <v>584188</v>
       </c>
       <c r="R17" t="n">
-        <v>6400866</v>
+        <v>6400848</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -1556,56 +1556,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725840</v>
+        <v>129719199</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>96386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584291</v>
+        <v>584216</v>
       </c>
       <c r="R10" t="n">
-        <v>6400891</v>
+        <v>6400895</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,40 +1624,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129719199</v>
+        <v>129719187</v>
       </c>
       <c r="B11" t="n">
-        <v>96386</v>
+        <v>92881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,37 +1674,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584216</v>
+        <v>584220</v>
       </c>
       <c r="R11" t="n">
-        <v>6400895</v>
+        <v>6400901</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,57 +1779,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129719187</v>
+        <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>92881</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584220</v>
+        <v>584291</v>
       </c>
       <c r="R12" t="n">
-        <v>6400901</v>
+        <v>6400891</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1846,39 +1855,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -4183,7 +4183,7 @@
         <v>129750113</v>
       </c>
       <c r="B34" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>129750075</v>
       </c>
       <c r="B35" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>129750063</v>
       </c>
       <c r="B36" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>129750085</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129719126</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129726111</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129726009</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129719496</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129720327</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>129726153</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129725784</v>
+        <v>129726121</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584306</v>
+        <v>584219</v>
       </c>
       <c r="R8" t="n">
-        <v>6400876</v>
+        <v>6401024</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726121</v>
+        <v>129725784</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584219</v>
+        <v>584306</v>
       </c>
       <c r="R9" t="n">
-        <v>6401024</v>
+        <v>6400876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>129719199</v>
       </c>
       <c r="B10" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129719187</v>
       </c>
       <c r="B11" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,57 +1885,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129719583</v>
+        <v>129726204</v>
       </c>
       <c r="B13" t="n">
-        <v>91620</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584209</v>
+        <v>584205</v>
       </c>
       <c r="R13" t="n">
-        <v>6400866</v>
+        <v>6401040</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,39 +1961,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2004,7 +1994,7 @@
         <v>129726185</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,56 +2097,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726204</v>
+        <v>129719984</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>96390</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584205</v>
+        <v>584188</v>
       </c>
       <c r="R15" t="n">
-        <v>6401040</v>
+        <v>6400848</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,86 +2174,96 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726214</v>
+        <v>129719583</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>91623</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584178</v>
+        <v>584209</v>
       </c>
       <c r="R16" t="n">
-        <v>6400881</v>
+        <v>6400866</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2289,87 +2290,95 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129719984</v>
+        <v>129726214</v>
       </c>
       <c r="B17" t="n">
-        <v>96386</v>
+        <v>98794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584188</v>
+        <v>584178</v>
       </c>
       <c r="R17" t="n">
-        <v>6400848</v>
+        <v>6400881</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2396,39 +2405,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2438,7 +2438,7 @@
         <v>129725705</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>129719448</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129719258</v>
+        <v>129726099</v>
       </c>
       <c r="B20" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,29 +2684,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584215</v>
+        <v>584229</v>
       </c>
       <c r="R20" t="n">
-        <v>6400897</v>
+        <v>6401032</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,49 +2732,40 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726099</v>
+        <v>129719258</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,28 +2790,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584229</v>
+        <v>584215</v>
       </c>
       <c r="R21" t="n">
-        <v>6401032</v>
+        <v>6400897</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2848,30 +2839,39 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
         <v>129725819</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129725803</v>
       </c>
       <c r="B23" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129726168</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>129726194</v>
       </c>
       <c r="B25" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129718908</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129726049</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129725774</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129719185</v>
       </c>
       <c r="B29" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129726072</v>
       </c>
       <c r="B30" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726136</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129726176</v>
       </c>
       <c r="B32" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>129719084</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -2435,56 +2435,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129725705</v>
+        <v>129719448</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>98794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 56162, Lilla fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584429</v>
+        <v>584201</v>
       </c>
       <c r="R18" t="n">
-        <v>6400936</v>
+        <v>6400891</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2511,9 +2512,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,69 +2539,68 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129719448</v>
+        <v>129725705</v>
       </c>
       <c r="B19" t="n">
-        <v>98794</v>
+        <v>57734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla fårhult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584201</v>
+        <v>584429</v>
       </c>
       <c r="R19" t="n">
-        <v>6400891</v>
+        <v>6400936</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,19 +2627,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,12 +2644,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129719126</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129726111</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129726009</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129719496</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129720327</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>129726153</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129726121</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>129725784</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129719199</v>
+        <v>129719187</v>
       </c>
       <c r="B10" t="n">
-        <v>96390</v>
+        <v>92887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,37 +1567,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584216</v>
+        <v>584220</v>
       </c>
       <c r="R10" t="n">
-        <v>6400895</v>
+        <v>6400901</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129719187</v>
+        <v>129719199</v>
       </c>
       <c r="B11" t="n">
-        <v>92884</v>
+        <v>96393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,46 +1683,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584220</v>
+        <v>584216</v>
       </c>
       <c r="R11" t="n">
-        <v>6400901</v>
+        <v>6400895</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,7 +1782,7 @@
         <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>129726204</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>129726185</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,57 +2097,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129719984</v>
+        <v>129726214</v>
       </c>
       <c r="B15" t="n">
-        <v>96390</v>
+        <v>98797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584188</v>
+        <v>584178</v>
       </c>
       <c r="R15" t="n">
-        <v>6400848</v>
+        <v>6400881</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,96 +2173,87 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129719583</v>
+        <v>129719984</v>
       </c>
       <c r="B16" t="n">
-        <v>91623</v>
+        <v>96393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584209</v>
+        <v>584188</v>
       </c>
       <c r="R16" t="n">
-        <v>6400866</v>
+        <v>6400848</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2329,56 +2319,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726214</v>
+        <v>129719583</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>91626</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584178</v>
+        <v>584209</v>
       </c>
       <c r="R17" t="n">
-        <v>6400881</v>
+        <v>6400866</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2405,87 +2396,95 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129719448</v>
+        <v>129725705</v>
       </c>
       <c r="B18" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla fårhult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584201</v>
+        <v>584429</v>
       </c>
       <c r="R18" t="n">
-        <v>6400891</v>
+        <v>6400936</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,19 +2511,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,68 +2528,69 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129725705</v>
+        <v>129719448</v>
       </c>
       <c r="B19" t="n">
-        <v>57734</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 56162, Lilla fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584429</v>
+        <v>584201</v>
       </c>
       <c r="R19" t="n">
-        <v>6400936</v>
+        <v>6400891</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,9 +2617,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,12 +2644,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
         <v>129726099</v>
       </c>
       <c r="B20" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>129719258</v>
       </c>
       <c r="B21" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>129725819</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129725803</v>
       </c>
       <c r="B23" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129726168</v>
       </c>
       <c r="B24" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>129726194</v>
       </c>
       <c r="B25" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129718908</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129726049</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129725774</v>
       </c>
       <c r="B28" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129719185</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129726072</v>
       </c>
       <c r="B30" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726136</v>
       </c>
       <c r="B31" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129726176</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>129719084</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129750113</v>
       </c>
       <c r="B34" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>129750075</v>
       </c>
       <c r="B35" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>129750063</v>
       </c>
       <c r="B36" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,44 +4498,44 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129750211</v>
+        <v>129750085</v>
       </c>
       <c r="B37" t="n">
-        <v>56710</v>
+        <v>57898</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100045</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>sträckande V</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584363</v>
+        <v>584096</v>
       </c>
       <c r="R37" t="n">
-        <v>6400913</v>
+        <v>6400801</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4575,22 +4575,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,44 +4607,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129750085</v>
+        <v>129750211</v>
       </c>
       <c r="B38" t="n">
-        <v>57895</v>
+        <v>56713</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100045</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>sträckande V</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4664,13 +4654,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584096</v>
+        <v>584363</v>
       </c>
       <c r="R38" t="n">
-        <v>6400801</v>
+        <v>6400913</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4694,12 +4684,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -1556,57 +1556,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129719187</v>
+        <v>129725840</v>
       </c>
       <c r="B10" t="n">
-        <v>92887</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584220</v>
+        <v>584291</v>
       </c>
       <c r="R10" t="n">
-        <v>6400901</v>
+        <v>6400891</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,39 +1632,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1779,56 +1769,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725840</v>
+        <v>129719187</v>
       </c>
       <c r="B12" t="n">
-        <v>98797</v>
+        <v>92887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584291</v>
+        <v>584220</v>
       </c>
       <c r="R12" t="n">
-        <v>6400891</v>
+        <v>6400901</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,30 +1846,39 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129719126</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129726111</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129719496</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129720327</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>129726153</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726121</v>
+        <v>129725784</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584219</v>
+        <v>584306</v>
       </c>
       <c r="R8" t="n">
-        <v>6401024</v>
+        <v>6400876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129725784</v>
+        <v>129726121</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584306</v>
+        <v>584219</v>
       </c>
       <c r="R9" t="n">
-        <v>6400876</v>
+        <v>6401024</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,56 +1556,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725840</v>
+        <v>129719199</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>96394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584291</v>
+        <v>584216</v>
       </c>
       <c r="R10" t="n">
-        <v>6400891</v>
+        <v>6400895</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,40 +1624,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129719199</v>
+        <v>129719187</v>
       </c>
       <c r="B11" t="n">
-        <v>96393</v>
+        <v>92888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,37 +1674,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584216</v>
+        <v>584220</v>
       </c>
       <c r="R11" t="n">
-        <v>6400895</v>
+        <v>6400901</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,57 +1779,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129719187</v>
+        <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>92887</v>
+        <v>98798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584220</v>
+        <v>584291</v>
       </c>
       <c r="R12" t="n">
-        <v>6400901</v>
+        <v>6400891</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1846,95 +1855,87 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726204</v>
+        <v>129719984</v>
       </c>
       <c r="B13" t="n">
-        <v>98797</v>
+        <v>96394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584205</v>
+        <v>584188</v>
       </c>
       <c r="R13" t="n">
-        <v>6401040</v>
+        <v>6400848</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,86 +1962,96 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726185</v>
+        <v>129719583</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>91627</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584229</v>
+        <v>584209</v>
       </c>
       <c r="R14" t="n">
-        <v>6401013</v>
+        <v>6400866</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,40 +2078,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726214</v>
+        <v>129726185</v>
       </c>
       <c r="B15" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584178</v>
+        <v>584229</v>
       </c>
       <c r="R15" t="n">
-        <v>6400881</v>
+        <v>6401013</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,57 +2223,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129719984</v>
+        <v>129726214</v>
       </c>
       <c r="B16" t="n">
-        <v>96393</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584188</v>
+        <v>584178</v>
       </c>
       <c r="R16" t="n">
-        <v>6400848</v>
+        <v>6400881</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,96 +2299,86 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129719583</v>
+        <v>129726204</v>
       </c>
       <c r="B17" t="n">
-        <v>91626</v>
+        <v>98798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584209</v>
+        <v>584205</v>
       </c>
       <c r="R17" t="n">
-        <v>6400866</v>
+        <v>6401040</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2396,39 +2405,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
         <v>129719448</v>
       </c>
       <c r="B19" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726099</v>
+        <v>129719258</v>
       </c>
       <c r="B20" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,28 +2684,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584229</v>
+        <v>584215</v>
       </c>
       <c r="R20" t="n">
-        <v>6401032</v>
+        <v>6400897</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,40 +2733,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129719258</v>
+        <v>129726099</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,29 +2800,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584215</v>
+        <v>584229</v>
       </c>
       <c r="R21" t="n">
-        <v>6400897</v>
+        <v>6401032</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2839,39 +2848,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
         <v>129725819</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129725803</v>
       </c>
       <c r="B23" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129726168</v>
       </c>
       <c r="B24" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>129726194</v>
       </c>
       <c r="B25" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129718908</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129726049</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129725774</v>
       </c>
       <c r="B28" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3630,10 +3630,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129719185</v>
+        <v>129726072</v>
       </c>
       <c r="B29" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3658,29 +3658,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584220</v>
+        <v>584237</v>
       </c>
       <c r="R29" t="n">
-        <v>6400901</v>
+        <v>6401043</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3707,49 +3706,40 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726072</v>
+        <v>129719185</v>
       </c>
       <c r="B30" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,28 +3764,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584237</v>
+        <v>584220</v>
       </c>
       <c r="R30" t="n">
-        <v>6401043</v>
+        <v>6400901</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3822,30 +3813,39 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
         <v>129726136</v>
       </c>
       <c r="B31" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129726176</v>
       </c>
       <c r="B32" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>129719084</v>
       </c>
       <c r="B33" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129750113</v>
       </c>
       <c r="B34" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>129750075</v>
       </c>
       <c r="B35" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>129750063</v>
       </c>
       <c r="B36" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,44 +4498,44 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129750085</v>
+        <v>129750211</v>
       </c>
       <c r="B37" t="n">
-        <v>57898</v>
+        <v>56713</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>100045</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>sträckande V</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584096</v>
+        <v>584363</v>
       </c>
       <c r="R37" t="n">
-        <v>6400801</v>
+        <v>6400913</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4575,12 +4575,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4607,44 +4617,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129750211</v>
+        <v>129750085</v>
       </c>
       <c r="B38" t="n">
-        <v>56713</v>
+        <v>57898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100045</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>sträckande V</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4654,13 +4664,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584363</v>
+        <v>584096</v>
       </c>
       <c r="R38" t="n">
-        <v>6400913</v>
+        <v>6400801</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4684,22 +4694,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129719126</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129726111</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129726009</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129719496</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129720327</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>129726153</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129725784</v>
+        <v>129726121</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584306</v>
+        <v>584219</v>
       </c>
       <c r="R8" t="n">
-        <v>6400876</v>
+        <v>6401024</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726121</v>
+        <v>129725784</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584219</v>
+        <v>584306</v>
       </c>
       <c r="R9" t="n">
-        <v>6401024</v>
+        <v>6400876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>129719199</v>
       </c>
       <c r="B10" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129719187</v>
       </c>
       <c r="B11" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>129725840</v>
       </c>
       <c r="B12" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>129719984</v>
       </c>
       <c r="B13" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>129719583</v>
       </c>
       <c r="B14" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726185</v>
+        <v>129726204</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584229</v>
+        <v>584205</v>
       </c>
       <c r="R15" t="n">
-        <v>6401013</v>
+        <v>6401040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726214</v>
+        <v>129726185</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584178</v>
+        <v>584229</v>
       </c>
       <c r="R16" t="n">
-        <v>6400881</v>
+        <v>6401013</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726204</v>
+        <v>129726214</v>
       </c>
       <c r="B17" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584205</v>
+        <v>584178</v>
       </c>
       <c r="R17" t="n">
-        <v>6401040</v>
+        <v>6400881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2543,7 +2543,7 @@
         <v>129719448</v>
       </c>
       <c r="B19" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129719258</v>
+        <v>129726099</v>
       </c>
       <c r="B20" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,29 +2684,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584215</v>
+        <v>584229</v>
       </c>
       <c r="R20" t="n">
-        <v>6400897</v>
+        <v>6401032</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,49 +2732,40 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726099</v>
+        <v>129719258</v>
       </c>
       <c r="B21" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,28 +2790,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584229</v>
+        <v>584215</v>
       </c>
       <c r="R21" t="n">
-        <v>6401032</v>
+        <v>6400897</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2848,30 +2839,39 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
         <v>129725819</v>
       </c>
       <c r="B22" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129725803</v>
       </c>
       <c r="B23" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129726168</v>
       </c>
       <c r="B24" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>129726194</v>
       </c>
       <c r="B25" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129718908</v>
       </c>
       <c r="B26" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129726049</v>
       </c>
       <c r="B27" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129725774</v>
       </c>
       <c r="B28" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3630,10 +3630,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129726072</v>
+        <v>129719185</v>
       </c>
       <c r="B29" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3658,28 +3658,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584237</v>
+        <v>584220</v>
       </c>
       <c r="R29" t="n">
-        <v>6401043</v>
+        <v>6400901</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3706,40 +3707,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129719185</v>
+        <v>129726072</v>
       </c>
       <c r="B30" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,29 +3774,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584220</v>
+        <v>584237</v>
       </c>
       <c r="R30" t="n">
-        <v>6400901</v>
+        <v>6401043</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3813,39 +3822,30 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
         <v>129726136</v>
       </c>
       <c r="B31" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129726176</v>
       </c>
       <c r="B32" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>129719084</v>
       </c>
       <c r="B33" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129750113</v>
       </c>
       <c r="B34" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>129750075</v>
       </c>
       <c r="B35" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>129750063</v>
       </c>
       <c r="B36" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>129750085</v>
       </c>
       <c r="B38" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56162-2025 artfynd.xlsx
+++ b/artfynd/A 56162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129719126</v>
+        <v>129719199</v>
       </c>
       <c r="B2" t="n">
-        <v>98820</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584215</v>
+        <v>584216</v>
       </c>
       <c r="R2" t="n">
-        <v>6400918</v>
+        <v>6400895</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,56 +782,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726111</v>
+        <v>129719984</v>
       </c>
       <c r="B3" t="n">
-        <v>98820</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Fårhultsjön, Fårhultsjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584229</v>
+        <v>584188</v>
       </c>
       <c r="R3" t="n">
-        <v>6401025</v>
+        <v>6400848</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,76 +859,77 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726009</v>
+        <v>129725803</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584277</v>
+        <v>584282</v>
       </c>
       <c r="R4" t="n">
-        <v>6400915</v>
+        <v>6400856</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,6 +981,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,42 +1000,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129719496</v>
+        <v>129719187</v>
       </c>
       <c r="B5" t="n">
-        <v>98820</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1050,13 +1044,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584200</v>
+        <v>584220</v>
       </c>
       <c r="R5" t="n">
-        <v>6400871</v>
+        <v>6400901</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,54 +1116,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129720327</v>
+        <v>129719583</v>
       </c>
       <c r="B6" t="n">
-        <v>98820</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584280</v>
+        <v>584209</v>
       </c>
       <c r="R6" t="n">
-        <v>6400833</v>
+        <v>6400866</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1201,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,53 +1232,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726153</v>
+        <v>129725705</v>
       </c>
       <c r="B7" t="n">
-        <v>98820</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>A 56162, Lilla fårhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584245</v>
+        <v>584429</v>
       </c>
       <c r="R7" t="n">
-        <v>6401045</v>
+        <v>6400936</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1319,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,42 +1337,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726121</v>
+        <v>129726009</v>
       </c>
       <c r="B8" t="n">
-        <v>98820</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1387,13 +1384,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584219</v>
+        <v>584277</v>
       </c>
       <c r="R8" t="n">
-        <v>6401024</v>
+        <v>6400915</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,7 +1428,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1450,56 +1446,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129725784</v>
+        <v>129750085</v>
       </c>
       <c r="B9" t="n">
-        <v>98820</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>A 56162, L Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584306</v>
+        <v>584096</v>
       </c>
       <c r="R9" t="n">
-        <v>6400876</v>
+        <v>6400801</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,7 +1537,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1556,48 +1555,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129719199</v>
+        <v>129718908</v>
       </c>
       <c r="B10" t="n">
-        <v>96416</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584216</v>
+        <v>584253</v>
       </c>
       <c r="R10" t="n">
-        <v>6400895</v>
+        <v>6400928</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,42 +1671,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129719187</v>
+        <v>129719084</v>
       </c>
       <c r="B11" t="n">
-        <v>92910</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1707,13 +1715,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584220</v>
+        <v>584224</v>
       </c>
       <c r="R11" t="n">
-        <v>6400901</v>
+        <v>6400911</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,7 +1750,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1760,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,10 +1787,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725840</v>
+        <v>129719126</v>
       </c>
       <c r="B12" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,28 +1815,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584291</v>
+        <v>584215</v>
       </c>
       <c r="R12" t="n">
-        <v>6400891</v>
+        <v>6400918</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,87 +1864,96 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129719984</v>
+        <v>129719185</v>
       </c>
       <c r="B13" t="n">
-        <v>96416</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fårhultsjön, Fårhultsjön, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584188</v>
+        <v>584220</v>
       </c>
       <c r="R13" t="n">
-        <v>6400848</v>
+        <v>6400901</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1974,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,42 +2019,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129719583</v>
+        <v>129719258</v>
       </c>
       <c r="B14" t="n">
-        <v>91649</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2045,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584209</v>
+        <v>584215</v>
       </c>
       <c r="R14" t="n">
-        <v>6400866</v>
+        <v>6400897</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2080,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2090,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726204</v>
+        <v>129719448</v>
       </c>
       <c r="B15" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,28 +2163,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584205</v>
+        <v>584201</v>
       </c>
       <c r="R15" t="n">
-        <v>6401040</v>
+        <v>6400891</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,40 +2212,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726185</v>
+        <v>129719496</v>
       </c>
       <c r="B16" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,28 +2279,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Ängnässjön, Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584229</v>
+        <v>584200</v>
       </c>
       <c r="R16" t="n">
-        <v>6401013</v>
+        <v>6400871</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2299,40 +2328,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726214</v>
+        <v>129720327</v>
       </c>
       <c r="B17" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,28 +2395,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 56162, Lilla Fårhult, Sm</t>
+          <t>Lilla Fårhult, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584178</v>
+        <v>584280</v>
       </c>
       <c r="R17" t="n">
-        <v>6400881</v>
+        <v>6400833</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2405,83 +2444,96 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129725705</v>
+        <v>129725774</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 56162, Lilla fårhult, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584429</v>
+        <v>584304</v>
       </c>
       <c r="R18" t="n">
-        <v>6400936</v>
+        <v>6400874</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,6 +2574,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2540,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129719448</v>
+        <v>129725784</v>
       </c>
       <c r="B19" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,29 +2621,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584201</v>
+        <v>584306</v>
       </c>
       <c r="R19" t="n">
-        <v>6400891</v>
+        <v>6400876</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,49 +2669,40 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726099</v>
+        <v>129725819</v>
       </c>
       <c r="B20" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584229</v>
+        <v>584294</v>
       </c>
       <c r="R20" t="n">
-        <v>6401032</v>
+        <v>6400890</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2762,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129719258</v>
+        <v>129725840</v>
       </c>
       <c r="B21" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,29 +2833,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584215</v>
+        <v>584291</v>
       </c>
       <c r="R21" t="n">
-        <v>6400897</v>
+        <v>6400891</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2839,49 +2881,40 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129725819</v>
+        <v>129726049</v>
       </c>
       <c r="B22" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584294</v>
+        <v>584232</v>
       </c>
       <c r="R22" t="n">
-        <v>6400890</v>
+        <v>6401020</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2984,36 +3017,40 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725803</v>
+        <v>129726072</v>
       </c>
       <c r="B23" t="n">
-        <v>96416</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3023,10 +3060,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584282</v>
+        <v>584237</v>
       </c>
       <c r="R23" t="n">
-        <v>6400856</v>
+        <v>6401043</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3086,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129726168</v>
+        <v>129726099</v>
       </c>
       <c r="B24" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,10 +3166,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584230</v>
+        <v>584229</v>
       </c>
       <c r="R24" t="n">
-        <v>6401024</v>
+        <v>6401032</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726194</v>
+        <v>129726111</v>
       </c>
       <c r="B25" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584208</v>
+        <v>584229</v>
       </c>
       <c r="R25" t="n">
-        <v>6401031</v>
+        <v>6401025</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3298,10 +3335,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129718908</v>
+        <v>129726121</v>
       </c>
       <c r="B26" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,29 +3363,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584253</v>
+        <v>584219</v>
       </c>
       <c r="R26" t="n">
-        <v>6400928</v>
+        <v>6401024</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3375,49 +3411,40 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129726049</v>
+        <v>129726136</v>
       </c>
       <c r="B27" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,10 +3484,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584232</v>
+        <v>584248</v>
       </c>
       <c r="R27" t="n">
-        <v>6401020</v>
+        <v>6401045</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3520,10 +3547,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129725774</v>
+        <v>129726153</v>
       </c>
       <c r="B28" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3548,11 +3575,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3567,10 +3590,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584304</v>
+        <v>584245</v>
       </c>
       <c r="R28" t="n">
-        <v>6400874</v>
+        <v>6401045</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3630,10 +3653,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129719185</v>
+        <v>129726168</v>
       </c>
       <c r="B29" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3658,29 +3681,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584220</v>
+        <v>584230</v>
       </c>
       <c r="R29" t="n">
-        <v>6400901</v>
+        <v>6401024</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3707,49 +3729,40 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726072</v>
+        <v>129726176</v>
       </c>
       <c r="B30" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3789,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584237</v>
+        <v>584227</v>
       </c>
       <c r="R30" t="n">
-        <v>6401043</v>
+        <v>6401014</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3852,10 +3865,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726136</v>
+        <v>129726185</v>
       </c>
       <c r="B31" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3895,10 +3908,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584248</v>
+        <v>584229</v>
       </c>
       <c r="R31" t="n">
-        <v>6401045</v>
+        <v>6401013</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3958,10 +3971,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726176</v>
+        <v>129726194</v>
       </c>
       <c r="B32" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,10 +4014,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584227</v>
+        <v>584208</v>
       </c>
       <c r="R32" t="n">
-        <v>6401014</v>
+        <v>6401031</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4064,10 +4077,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129719084</v>
+        <v>129726204</v>
       </c>
       <c r="B33" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4092,29 +4105,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ängnässjön, Ängnässjön, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584224</v>
+        <v>584205</v>
       </c>
       <c r="R33" t="n">
-        <v>6400911</v>
+        <v>6401040</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4141,71 +4153,62 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129750113</v>
+        <v>129726214</v>
       </c>
       <c r="B34" t="n">
-        <v>105896</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4219,14 +4222,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 56162, L Fårhult, Sm</t>
+          <t>A 56162, Lilla Fårhult, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583930</v>
+        <v>584178</v>
       </c>
       <c r="R34" t="n">
-        <v>6400825</v>
+        <v>6400881</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4253,12 +4256,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4286,10 +4289,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129750075</v>
+        <v>129750063</v>
       </c>
       <c r="B35" t="n">
-        <v>105896</v>
+        <v>106243</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4329,10 +4332,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584096</v>
+        <v>584130</v>
       </c>
       <c r="R35" t="n">
-        <v>6400801</v>
+        <v>6400829</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4392,10 +4395,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129750063</v>
+        <v>129750075</v>
       </c>
       <c r="B36" t="n">
-        <v>105896</v>
+        <v>106243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4435,10 +4438,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584130</v>
+        <v>584096</v>
       </c>
       <c r="R36" t="n">
-        <v>6400829</v>
+        <v>6400801</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4498,10 +4501,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129750211</v>
+        <v>129750113</v>
       </c>
       <c r="B37" t="n">
-        <v>56713</v>
+        <v>106243</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4509,35 +4512,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100045</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>sträckande V</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4545,13 +4544,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584363</v>
+        <v>583930</v>
       </c>
       <c r="R37" t="n">
-        <v>6400913</v>
+        <v>6400825</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4575,22 +4574,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4599,6 +4588,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4614,115 +4604,6 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>129750085</v>
-      </c>
-      <c r="B38" t="n">
-        <v>57899</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>A 56162, L Fårhult, Sm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>584096</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6400801</v>
-      </c>
-      <c r="S38" t="n">
-        <v>25</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Gladhammar</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
